--- a/evaluation/gemini_realset.xlsx
+++ b/evaluation/gemini_realset.xlsx
@@ -333,7 +333,7 @@
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.2700719993472824</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.15833333333333333</v>
+        <v>0.5391666666666667</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.09343850875788193</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.13888888888888892</v>
+        <v>0.5012626262626263</v>
       </c>
     </row>
     <row r="3">
@@ -401,7 +401,7 @@
         <v>0.18376033968927596</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.3575892857142857</v>
+        <v>0.6606128246753247</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         <v>0.8106535524993804</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.3168560606060606</v>
+        <v>0.5945982430689878</v>
       </c>
     </row>
     <row r="8">
@@ -469,7 +469,7 @@
         <v>0.5249195423594161</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.05433006535947712</v>
+        <v>0.4724775326797386</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         <v>0.9552965054323246</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.4083333333333333</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         <v>0.7536047165172917</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -553,7 +553,7 @@
         <v>0.1348692525566187</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.03935185185185186</v>
+        <v>0.5196759259259259</v>
       </c>
     </row>
     <row r="14">
@@ -569,7 +569,7 @@
         <v>0.0</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.1842261904761905</v>
+        <v>0.5504464285714286</v>
       </c>
     </row>
     <row r="15">
@@ -585,7 +585,7 @@
         <v>0.563359107381999</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.6157024793388429</v>
+        <v>0.7708142026323844</v>
       </c>
     </row>
     <row r="16">
@@ -601,7 +601,7 @@
         <v>0.3201288845762984</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.12797619047619047</v>
+        <v>0.34834828481155494</v>
       </c>
     </row>
     <row r="17">
@@ -617,7 +617,7 @@
         <v>0.07621241953096713</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.03131313131313132</v>
+        <v>0.4668760778516876</v>
       </c>
     </row>
     <row r="18">
@@ -633,7 +633,7 @@
         <v>0.18952747084116808</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.052083333333333336</v>
+        <v>0.4367559523809524</v>
       </c>
     </row>
     <row r="19">
@@ -649,7 +649,7 @@
         <v>0.1589718787820826</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.5444444444444444</v>
       </c>
     </row>
     <row r="20">
@@ -685,7 +685,7 @@
         <v>0.0</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.25</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="22">

--- a/evaluation/gemini_realset.xlsx
+++ b/evaluation/gemini_realset.xlsx
@@ -333,7 +333,7 @@
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.2700719993472824</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.5391666666666667</v>
+        <v>0.14566666666666667</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.09343850875788193</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.5012626262626263</v>
+        <v>0.11994949494949499</v>
       </c>
     </row>
     <row r="3">
@@ -401,7 +401,7 @@
         <v>0.18376033968927596</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.6606128246753247</v>
+        <v>0.34458603896103895</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         <v>0.8106535524993804</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.5945982430689878</v>
+        <v>0.27640635074145714</v>
       </c>
     </row>
     <row r="8">
@@ -469,7 +469,7 @@
         <v>0.5249195423594161</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.4724775326797386</v>
+        <v>0.04838771446078431</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         <v>0.9552965054323246</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.6375</v>
+        <v>0.3538888888888889</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         <v>0.7536047165172917</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -553,7 +553,7 @@
         <v>0.1348692525566187</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.5196759259259259</v>
+        <v>0.03935185185185186</v>
       </c>
     </row>
     <row r="14">
@@ -569,7 +569,7 @@
         <v>0.0</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.5504464285714286</v>
+        <v>0.16887400793650795</v>
       </c>
     </row>
     <row r="15">
@@ -585,7 +585,7 @@
         <v>0.563359107381999</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.7708142026323844</v>
+        <v>0.5700948882767064</v>
       </c>
     </row>
     <row r="16">
@@ -601,7 +601,7 @@
         <v>0.3201288845762984</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.34834828481155494</v>
+        <v>0.07278266756939741</v>
       </c>
     </row>
     <row r="17">
@@ -617,7 +617,7 @@
         <v>0.07621241953096713</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.4668760778516876</v>
+        <v>0.028258191672825828</v>
       </c>
     </row>
     <row r="18">
@@ -633,7 +633,7 @@
         <v>0.18952747084116808</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.4367559523809524</v>
+        <v>0.042782738095238096</v>
       </c>
     </row>
     <row r="19">
@@ -649,7 +649,7 @@
         <v>0.1589718787820826</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.5444444444444444</v>
+        <v>0.08888888888888889</v>
       </c>
     </row>
     <row r="20">
@@ -685,7 +685,7 @@
         <v>0.0</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.425</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="22">
